--- a/Teileliste.xlsx
+++ b/Teileliste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Platinen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gallitschke\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512ED08C-CAB6-47B7-B81D-9CE0401E9BF4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E25E9E-C331-4662-9273-194C4CC14443}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="4" xr2:uid="{DCE56310-0F41-4EC1-B508-74A71DCA75A2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" activeTab="3" xr2:uid="{DCE56310-0F41-4EC1-B508-74A71DCA75A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Einhorn" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>Stück</t>
   </si>
@@ -100,33 +100,9 @@
     <t>Abhänging von der LED Farbe: Alle L6.3</t>
   </si>
   <si>
-    <t>https://www.conrad.de/de/p/vitrohm-pos100jt-52-82raa-pos100jt-52-82raa-metallschicht-widerstand-82-tht-0207-1-w-5-1-st-3359374.html?insert=YD</t>
-  </si>
-  <si>
-    <t>Gelb: 47</t>
-  </si>
-  <si>
-    <t>Rot: 82</t>
-  </si>
-  <si>
-    <t>https://www.conrad.de/de/p/vitrohm-pos100jt-52-47raa-pos100jt-52-47raa-metallschicht-widerstand-47-tht-0207-1-w-5-1-st-box-3359222.html</t>
-  </si>
-  <si>
-    <t>Grün: 47</t>
-  </si>
-  <si>
-    <t>Blau: 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGB, Lila, Pink: 0 </t>
-  </si>
-  <si>
     <t>https://www.reichelt.com/de/en/shop/product/metal_film_resistor_0_00_ohm-184962</t>
   </si>
   <si>
-    <t>https://www.reichelt.com/de/en/shop/product/metal_film_resistor_6_20_ohm-11898</t>
-  </si>
-  <si>
     <t>https://www.reichelt.com/de/en/shop/product/electret_condenser_microphone_capsule-11357?search=mce%252010&amp;</t>
   </si>
   <si>
@@ -158,6 +134,15 @@
   </si>
   <si>
     <t>VitrOhm POS100JT-52-1KAA POS100JT-52-1KAA Metallschicht-Widerstand 1 kΩ THT 0207 1 W 5 % 1 St. kaufen</t>
+  </si>
+  <si>
+    <t>Rot: 200</t>
+  </si>
+  <si>
+    <t>Gelb, Grün, Orange: 180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGB, Lila, Pink, Blau: 0 </t>
   </si>
 </sst>
 </file>
@@ -548,7 +533,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D39B2E5-8180-4268-B1DB-F64DFB7D65BA}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
@@ -578,7 +563,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -603,10 +588,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -617,7 +602,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -689,61 +674,40 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>26</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="D14" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D8" r:id="rId1" xr:uid="{A6373690-8E12-4A89-A837-3A411D9602C9}"/>
-    <hyperlink ref="D15" r:id="rId2" xr:uid="{0404AF67-6A1A-4D1E-BF5B-00962F344DFA}"/>
+    <hyperlink ref="D13" r:id="rId2" xr:uid="{0404AF67-6A1A-4D1E-BF5B-00962F344DFA}"/>
     <hyperlink ref="D2" r:id="rId3" xr:uid="{6FE033F9-6283-4DBA-9B95-7F9EBC4BFF4F}"/>
     <hyperlink ref="D3" r:id="rId4" xr:uid="{755B224A-9E5A-4091-86D2-B45554AC5D9B}"/>
     <hyperlink ref="D4" r:id="rId5" xr:uid="{32C6C44B-5CCE-432E-902A-C2D74A43BB8C}"/>
     <hyperlink ref="D5" r:id="rId6" xr:uid="{658182F0-72A4-4B08-A38A-89DEAD17C11C}"/>
     <hyperlink ref="D6" r:id="rId7" location="productDownloads" xr:uid="{23FA6852-CFC7-46CE-87E1-00C1C821EEAC}"/>
     <hyperlink ref="D9" r:id="rId8" xr:uid="{ED7E847A-C219-4FB1-88FE-846BBB9451F0}"/>
-    <hyperlink ref="D11" r:id="rId9" xr:uid="{6DE53D5C-86CD-411C-AE9A-57A215C23867}"/>
-    <hyperlink ref="D12" r:id="rId10" xr:uid="{57E52027-8A86-4A17-BCA7-529AA68717DA}"/>
-    <hyperlink ref="D13" r:id="rId11" xr:uid="{251569C9-7453-47F3-AF35-854F70A56E0A}"/>
-    <hyperlink ref="D14" r:id="rId12" xr:uid="{E44052C0-E07D-43BB-B0A6-AD3BB01A74CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" copies="14" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" copies="14" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -785,13 +749,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -799,10 +763,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -816,7 +780,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -827,10 +791,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
